--- a/rover_platform_mbse/export/ROVER-A1-ROVER_GPS_HEADING-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_GPS_HEADING-SWRS-V-001.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_GPS_HEADING-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_GPS_HEADING-SWRS-V-001.xlsx
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
